--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20222.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -85,87 +85,54 @@
     <t>MAZAHUA</t>
   </si>
   <si>
-    <t>BACILIO</t>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>URBANO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>ZAVALETA</t>
-  </si>
-  <si>
-    <t>AGUIRRE</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>ESTRELLA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
     <t>GENARO RAFAEL</t>
   </si>
   <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>ALFREDO</t>
-  </si>
-  <si>
-    <t>MARIAM GUADALUPE</t>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>VICTOR GAMALIEL</t>
   </si>
   <si>
     <t>ELIEL</t>
   </si>
   <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
     <t>ALEXA</t>
   </si>
   <si>
@@ -173,9 +140,6 @@
   </si>
   <si>
     <t>NAOMI</t>
-  </si>
-  <si>
-    <t>VICTOR GAMALIEL</t>
   </si>
 </sst>
 </file>
@@ -628,16 +592,19 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -817,7 +784,7 @@
         <v>20</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -997,16 +964,19 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1094,7 +1064,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1132,10 +1102,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1149,22 +1119,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920336</v>
+        <v>20330051920097</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1172,39 +1142,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920263</v>
+        <v>20330051920244</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920344</v>
+        <v>20330051920345</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1213,190 +1183,75 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920345</v>
+        <v>20330051920296</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920348</v>
+        <v>20330051920297</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920355</v>
+        <v>20330051920312</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920382</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920296</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920297</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920312</v>
-      </c>
-      <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920244</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20222.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="47">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,12 @@
     <t>MAZAHUA</t>
   </si>
   <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
@@ -103,6 +109,12 @@
     <t>ACEVEDO</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>EVARISTO</t>
   </si>
   <si>
@@ -122,6 +134,12 @@
   </si>
   <si>
     <t>GENARO RAFAEL</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>MONICA</t>
   </si>
   <si>
     <t>ALDAIR ALAN</t>
@@ -1064,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1102,10 +1120,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1119,22 +1137,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920097</v>
+        <v>20330051920174</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1142,68 +1160,68 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920244</v>
+        <v>20330051920178</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920345</v>
+        <v>20330051920097</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920296</v>
+        <v>20330051920244</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1211,22 +1229,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920297</v>
+        <v>20330051920345</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1234,16 +1252,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920312</v>
+        <v>20330051920296</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1252,6 +1270,52 @@
         <v>14</v>
       </c>
       <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920297</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920312</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20222.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -82,79 +82,70 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
     <t>TORRES</t>
   </si>
   <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
     <t>ACEVEDO</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
     <t>PRADO</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>ELIEL</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
     <t>GENARO RAFAEL</t>
   </si>
   <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>VICTOR GAMALIEL</t>
-  </si>
-  <si>
-    <t>ELIEL</t>
-  </si>
-  <si>
     <t>ALEXA</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
   </si>
   <si>
     <t>NAOMI</t>
@@ -753,16 +744,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="H2">
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -776,16 +770,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>97.06</v>
+      </c>
+      <c r="H3">
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -799,16 +796,19 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -822,16 +822,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>94.44</v>
+      </c>
+      <c r="H5">
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -845,16 +848,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>82.14</v>
+      </c>
+      <c r="H6">
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -868,16 +874,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>93.75</v>
+      </c>
+      <c r="H7">
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -933,16 +942,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>83.33</v>
+        <v>90</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -959,16 +968,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -994,7 +1003,7 @@
         <v>90</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1020,7 +1029,7 @@
         <v>94.44</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1037,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>85.70999999999999</v>
+        <v>82.14</v>
       </c>
       <c r="H6">
         <v>7.4</v>
@@ -1063,16 +1072,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>90.63</v>
+        <v>93.75</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -1082,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1114,22 +1123,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920236</v>
+        <v>20330051920345</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1143,10 +1152,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1166,10 +1175,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1189,10 +1198,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1206,45 +1215,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920244</v>
+        <v>20330051920058</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920345</v>
+        <v>20330051920236</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1255,13 +1264,13 @@
         <v>20330051920296</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1275,16 +1284,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920297</v>
+        <v>20330051920312</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1293,29 +1302,6 @@
         <v>14</v>
       </c>
       <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920312</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20222.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20222.xlsx
@@ -85,42 +85,42 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
     <t>NAMORADO</t>
   </si>
   <si>
     <t>QUIRIZ</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
     <t>TORRES</t>
   </si>
   <si>
     <t>IXTLA</t>
   </si>
   <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
     <t>PRADO</t>
   </si>
   <si>
@@ -130,19 +130,19 @@
     <t>ELIEL</t>
   </si>
   <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
+    <t>GENARO RAFAEL</t>
+  </si>
+  <si>
     <t>LUZ ESTRELLA</t>
   </si>
   <si>
     <t>MONICA</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>GENARO RAFAEL</t>
   </si>
   <si>
     <t>ALEXA</t>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920174</v>
+        <v>20330051920097</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -1161,7 +1161,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920178</v>
+        <v>20330051920058</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1184,7 +1184,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1192,7 +1192,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920097</v>
+        <v>20330051920236</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1207,15 +1207,15 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920058</v>
+        <v>20330051920174</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1230,15 +1230,15 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920236</v>
+        <v>20330051920178</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1253,7 +1253,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>1</v>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20222.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20222.xlsx
@@ -88,18 +88,18 @@
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
     <t>TORRES</t>
   </si>
   <si>
@@ -109,18 +109,18 @@
     <t>EVARISTO</t>
   </si>
   <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>BELLO</t>
   </si>
   <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>PRADO</t>
   </si>
   <si>
@@ -133,16 +133,16 @@
     <t>ALDAIR ALAN</t>
   </si>
   <si>
+    <t>GENARO RAFAEL</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
     <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>GENARO RAFAEL</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>MONICA</t>
   </si>
   <si>
     <t>ALEXA</t>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920058</v>
+        <v>20330051920236</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1184,15 +1184,15 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920236</v>
+        <v>20330051920174</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1207,7 +1207,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920174</v>
+        <v>20330051920178</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1238,7 +1238,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920178</v>
+        <v>20330051920058</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1253,7 +1253,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>1</v>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20222.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -80,75 +80,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ELIEL</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>GENARO RAFAEL</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>ALEXA</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
   </si>
 </sst>
 </file>
@@ -942,16 +873,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -968,16 +899,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -994,16 +925,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1020,13 +951,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>8.800000000000001</v>
@@ -1046,16 +977,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>82.14</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1072,16 +1003,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1091,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1121,190 +1052,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920345</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920097</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920236</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920174</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920178</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920058</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920296</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920312</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20222.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20222.xlsx
@@ -977,13 +977,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>96.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>7.6</v>
